--- a/抽检表_标注者B.xlsx
+++ b/抽检表_标注者B.xlsx
@@ -479,19 +479,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +508,8 @@
           <t>填写说明：只需填黄色三列，用下拉选择 ✓ / ✗ / 存疑，有疑问时在备注列写一句原因。第4行为示例行（不计入统计）。请独立判定——不要参考另一位标注者的结果，也不要互相商量，否则一致性系数失去意义。
 【答案正确?】标准答案与原文是否相符（数值、行标签、年份、量纲）。相符✓，不符✗。
 【唯一合理答案?】在问题的字面表述下，标准答案是否是唯一站得住的答案。是✓；若一个称职的分析师可能给出另一个同样站得住的答案，判✗并在备注写出那个答案。常见歧义来源：①指标口径（归母净资产／所有者权益合计、营业收入／营业总收入）；②合并报表与母公司报表；③上年数是追溯调整后还是原披露数；④同一年数字在本年报与次年年报的上年同期栏都出现，取哪一处。
-注意这两列相互独立：答案可以完全正确，但问题本身有歧义（判 ✓ / ✗）。证据原文列是自动匹配的 gold 三元组；表名若读不出计量单位，请对照原PDF确认量纲。</t>
+注意这两列相互独立：答案可以完全正确，但问题本身有歧义。
+【同表相近行】列出了同一张表里口径相近的其他科目及其数值——判歧义时先看这一列，多数情况无需打开源PDF。仅当表名读不出计量单位、或需确认上年数是否追溯调整时，才需对照原PDF。</t>
         </is>
       </c>
     </row>
@@ -544,20 +546,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>同表相近行（判歧义用）</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>来源（文件@页）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>答案正确?</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>唯一合理答案?</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -596,22 +603,28 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>营业总收入 = 164,699百万元
+利息净收入 = 116,061百万元</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>000001_平安银行_2023年年度报告.pdf @15</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>数值与原文一致；「营业收入」在该表中口径唯一</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>数值与原文一致；该表虽有「营业总收入」，但本行两者同值，不构成歧义</t>
         </is>
       </c>
     </row>
@@ -647,12 +660,17 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 114,025,058,788.17</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -686,12 +704,22 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
+          <t>投资活动产生的现金流量净额 = (461,564.21)万元
+筹资活动产生的现金流量净额 = (3,681,316.43)万元
+经营活动现金流入小计 = 32,112,867.05万元
+经营活动现金流出小计 = 31,721,634.66万元
+投资活动现金流入小计 = 1,527,306.06万元
+投资活动现金流出小计 = 1,988,870.27万元</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
           <t>000002_万  科Ａ_2023年年度报告.pdf @29</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -725,12 +753,19 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>【三一重工 三一重工股份有限公司2024年年度报告】加权平均净资产收益率（%） = 8.54
+【三一重工 三一重工股份有限公司2024年年度报告】扣除非经常性损益后的加权平 均净资产收益率（%） = 7.62
+【三一重工 三一重工股份有限公司2024年年度报告】扣除非经常性损益后的基本每 股收益（元／股） = 0.6297</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -764,12 +799,18 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经常 性损益的净利润 = 3,126,760千元
+归属于上市公司股东的净资产 = 64,965,662千元</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -803,12 +844,20 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 24.13%
+归属于上市公司股东的净利润（千元） = 50,744,682
+经营活动产生的现金流量净额（千元） = 96,990,345
+资产总额（千元） = 786,658,123</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -842,12 +891,18 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 19.62%
+归属于上市公司股东的净资产（元） = 68,389,154,548.76</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -881,12 +936,18 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 20.30%
+归属于上市公司股东的净资产 （元） = 145,929,297,804.02</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -920,12 +981,17 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -959,12 +1025,17 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -998,12 +1069,21 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元
+营业利润 = 52,006,935,659.54元
+利润总额 = 52,386,185,416.63元
+归属于上市公司股 东的净资产 = 242,691,342,204.55元
+归属于上市公司股 东的每股净资产 = 21.00</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -1037,12 +1117,21 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元
+营业利润 = 52,006,935,659.54元
+利润总额 = 52,386,185,416.63元
+归属于上市公司股 东的净资产 = 242,691,342,204.55元
+归属于上市公司股 东的每股净资产 = 21.00</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -1076,12 +1165,18 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润（元） = 27,706,292,436.94
+归属于上市公司股东的净资产 （元） = 145,929,297,804.02</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -1115,12 +1210,18 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 11.58
+加权平均净资产收益率 = 24.13%</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -1154,12 +1255,17 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>300760_迈瑞医疗_2024年年度报告.pdf @21</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -1193,12 +1299,20 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平 均净资产收益率（%） = 19.32
+基本每股收益（元／股） = 3.01
+稀释每股收益（元／股） = 2.82
+扣除非经常性损益后的基本每 股收益（元／股） = 2.82</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -1232,12 +1346,17 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
+          <t>营业利润 = 52,006,935,659.54元</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -1271,12 +1390,18 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 5.71
+加权平均净资产收益率 = 16.14%</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -1310,12 +1435,17 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司 股东的净资产 = 201,330,025,517.69元</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2023年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -1349,12 +1479,18 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 24.13%
+归属于上市公司股东的净资产（千元） = 246,930,033</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -1388,12 +1524,17 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东 的扣除非经常性损益 的净利润 = 10,833,665,062.03元</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2023年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -1427,12 +1568,17 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 8,221,213千元</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -1466,12 +1612,17 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 18.80</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2022年年度报告.pdf @18</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1505,12 +1656,20 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 17.30%
+归属于上市公司股东的净利润（元） = 14,195,371,894.42
+经营活动产生的现金流量净额（元） = 25,339,411,083.10
+总资产（元） = 138,049,655,334.62</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2025年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -1544,12 +1703,20 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 59.51
+稀释每股收益（元／股） = 59.49
+加权平均净资产收益率（%） = 34.19
+扣除非经常性损益后的加权平 均净资产收益率（%） = 34.20</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2023年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -1583,12 +1750,18 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 17.30%
+归属于上市公司股东的净资产（元） = 83,348,185,885.62</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2025年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -1622,12 +1795,17 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（千元） = 246,930,033</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -1661,12 +1839,18 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公 司股东的扣除 非经常性损益 的净利润 = 74,752,564,425.52元
+归属于上市公 司股东的净资 产 = 215,668,571,607.43元</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2023年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
       <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -1700,12 +1884,17 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -1739,12 +1928,17 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 53,539,331,413.16元</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2023年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -1778,12 +1972,17 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润（元） = 27,706,292,436.94</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -1817,12 +2016,18 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经 常性损益的净利润 = 8,585,692,731.44元
+归属于上市公司股东的净资产 = 50,267,883,832.15元</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="6" t="inlineStr"/>
       <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -1856,12 +2061,17 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣 除非经常性损益的净利润 = 86,240,905,977.42元</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr"/>
       <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -1895,12 +2105,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 4,388,393千元</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2023年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -1934,12 +2149,22 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的每股净资产 = 21.00
+全面摊薄净资产收 益率 = 9.32%
+加权平均净资产收 益率 = 9.48%
+归属于上市公司股 东的净利润 = 22,617,778,516.45元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元
+经营活动产生的现 金流量净额 = 2,750,449,478.44元</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -1973,12 +2198,17 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净 资产 = 60,895,314,122.52元</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2024年年度报告（修订版）.pdf @11</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -2012,12 +2242,20 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 25.28%
+归属于上市公司股东的净利润（元） = 26,690,661,397.42
+经营活动产生的现金流量净额（元） = 24,431,136,261.48
+总资产（元） = 152,714,727,880.22</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -2051,12 +2289,17 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 10,026,171,076.03元</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2023年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -2090,12 +2333,18 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 4.92
+加权平均净资产收益率 = 22.23%</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -2129,12 +2378,20 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净利润 = 4,302,435,930.05元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 4,141,262,764.05元
+经营活动产生的现 金流量净额 = 7,643,665,074.52元
+总资产 = 43,784,506,635.76元</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -2168,12 +2425,17 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经 常性损益的净利润 = 8,585,692,731.44元</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -2207,12 +2469,17 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 111,029,299,000.00</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -2246,12 +2513,22 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
+          <t>投资活动产生的现金流量净额 = -13,509,510千元
+筹资活动产生的现金流量净额 = -10,854,881千元
+经营活动现金流入小计 = 343,767,987千元
+经营活动现金流出小计 = 309,110,159千元
+投资活动现金流入小计 = 102,953,948千元
+投资活动现金流出小计 = 116,463,458千元</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2022年年度报告.pdf @56</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -2285,12 +2562,17 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
+          <t>营业利润 = (45,643,796,280.61)元</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -2324,12 +2606,17 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
           <t>300760_迈瑞医疗_2023年年度报告.pdf @19</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2363,12 +2650,18 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 4,141,262,764.05元
+归属于上市公司股 东的净资产 = 40,465,795,358.69元</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -2402,12 +2695,18 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 22.23%
+归属于上市公司股东的净资产（千元） = 162,878,825</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -2441,12 +2740,19 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 5.20
+归属于上市公司股东的扣除非 经常性损益的净利润（元） = 27,706,292,436.94
+加权平均净资产收益率 = 20.30%</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -2480,12 +2786,20 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平均 净资产收益率（%） = 16.33
+基本每股收益（元／股） = 1.42
+稀释每股收益（元／股） = 1.42
+扣除非经常性损益后的基本每股 收益（元／股） = 1.43</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2023年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -2519,12 +2833,20 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净利润 = 9,431,064,679.78元
+归属于上市公司股东的扣除非经 常性损益的净利润 = 8,585,692,731.44元
+经营活动产生的现金流量净额 = 13,420,320,580.36元
+总资产 = 130,965,302,299.22元</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -2558,12 +2880,17 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -2597,12 +2924,20 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益（元／股） = 1.34
+稀释每股收益（元／股） = 1.48
+加权平均净资产收益率（%） = 19.23
+扣除非经常性损益后的加权平均净资产收益率（%） = 17.39</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -2636,12 +2971,20 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平均 净资产收益率（%） = 32.52
+基本每股收益（元／股） = 65.66
+稀释每股收益（元／股） = 65.66
+扣除非经常性损益后的基本每股 收益（元／股） = 65.64</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -2675,12 +3018,18 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收 益率 = 24.31%
+归属于上市公司股 东的净资产（元） = 19,815,886,930.86</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>300124_汇川技术_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="6" t="inlineStr"/>
       <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -2716,12 +3065,22 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 1.90
+扣除非经常性损益后的基本每股 收益（元／股） = 1.43
+稀释每股收益（元／股） = 1.95
+加权平均净资产收益率 （%） = 26.95
+扣除非经常性损益后的加权平 均净资产收益率（%） = 26.23
+加权平均净资产收益率（%） = 16.20</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2022年年度报告（修订版）.pdf @10; 601012_隆基绿能_2023年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -2755,12 +3114,17 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益 = 23.00%</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="6" t="inlineStr"/>
       <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -2796,12 +3160,17 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2023年年度报告.pdf @8; 603259_药明康德_2024年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr"/>
       <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -2837,12 +3206,17 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2024年度报告.pdf @7; 601088_中国神华_中国神华2025年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -2878,12 +3252,21 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经常性 损益的净利润 = -7,361,963,984.28元
+归属于上市公司股东的扣 除非经常性损益的净利润 = -8,747,230,737.94元
+利润总额 = -7,561,633,667.41元
+归属于上市公司股东的净资产 = 54,275,611,054.63元
+归属于上市公司股东的净 资产 = 60,895,314,122.52元</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2024年年度报告（修订版）.pdf @11; 601012_隆基绿能_2025年年度报告.pdf @13</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -2919,12 +3302,22 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益 = (4.17)
+扣除非经常性损益后归属于上 市公司股东的净利润 = (45,393,719,289.83)元
+净资产收益率（全面摊薄） = -24.41%
+净资产收益率（加权平均） = -21.82%
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元
+全面摊薄净资产收 益率 = 9.32%</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12; 000002_万科A_2024年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -2958,12 +3351,19 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净利润 = 21,309,033,980.94元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 21,392,344,535.58元
+经营活动产生的现 金流量净额 = 30,912,732,230.12元</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2022年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -2999,12 +3399,17 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2022年年度报告（修订版）.pdf @9; 601012_隆基绿能_2023年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -3038,12 +3443,17 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 114,025,058,788.17</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -3079,12 +3489,18 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 6,011,274,945.92元
+归属于上市公司股东的净资产 = 53,179,935,140.80元</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2023年年度报告.pdf @7; 600887_伊利股份_内蒙古伊利实业集团股份有限公司2024年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -3120,12 +3536,22 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净利润 = 9,606,749,135.07元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 9,747,587,804.59元
+经营活动产生的现 金流量净额 = 13,386,911,778.77元
+总资产 = 73,669,349,307.12元
+归属于上市公司股东的净 利润 = 8,813,713,033.51元
+归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7; 603259_药明康德_2023年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -3159,12 +3585,20 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 17.30%
+归属于上市公司股东的净利润（元） = 14,195,371,894.42
+经营活动产生的现金流量净额（元） = 25,339,411,083.10
+总资产（元） = 138,049,655,334.62</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2025年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -3198,12 +3632,21 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 20.30%
+归属于上市公司股东的净利润 （元） = 29,003,103,411.66
+归属于上市公司股东的扣除非 经常性损益的净利润（元） = 27,706,292,436.94
+经营活动产生的现金流量净额 （元） = 46,383,114,754.02
+总资产（元） = 391,371,999,819.49</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -3237,12 +3680,17 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -3278,12 +3726,17 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 5,333,989千元</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2023年年度报告.pdf @5; 600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -3319,12 +3772,19 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 21.34%
+归属于上市公司股东的净资产（元） = 69,327,010,925.99
+加权平均净资产收益 = 23.00%</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2022年年度报告.pdf @8; 002475_立讯精密_2024年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -3360,12 +3820,18 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
+          <t>扣除与主营业务无关的业务收入和不 具备商业实质的收入后的营业收入 = 69,156,038,920.71元
+扣除与主营业务无关的业 务收入和不具备商业实质 的收入后的营业收入 = 81,211,823,906.59元</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2024年年度报告（修订版）.pdf @11; 601012_隆基绿能_2025年年度报告.pdf @13</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -3401,12 +3867,17 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>归属于本公司股东 的扣除非经常性损 益的净利润 = 48,589百万元</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2024年度报告.pdf @7; 601088_中国神华_中国神华2025年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -3440,12 +3911,17 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 50,267,883,832.15元</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -3479,12 +3955,18 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 1.370
+加权平均净资产收益率 = 19.62%</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -3520,12 +4002,17 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
+          <t>归属于本公司股东 的扣除非经常性损 益的净利润 = 62,868百万元</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2022年度报告.pdf @7; 601088_中国神华_中国神华2023年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -3559,12 +4046,20 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 24.13%
+归属于上市公司股东的净利润（千元） = 50,744,682
+经营活动产生的现金流量净额（千元） = 96,990,345
+资产总额（千元） = 786,658,123</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
       <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -3600,12 +4095,19 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后归属于上 市公司股东的净利润 = (45,393,719,289.83)元
+营业利润 = (70,999,044,405.37)元
+利润总额 = (73,923,814,314.97)元</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11; 000002_万科A_2025年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" s="6" t="inlineStr"/>
       <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -3639,12 +4141,18 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 19.62%
+归属于上市公司股东的净资产（元） = 68,389,154,548.76</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="6" t="inlineStr"/>
       <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -3680,12 +4188,18 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 21.89
+资产总额 = 5,769,270百万元</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2023年年度报告.pdf @15; 000001_平安银行_2024年年度报告.pdf @16</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" s="6" t="inlineStr"/>
       <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -3719,12 +4233,17 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
       <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -3760,12 +4279,17 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 88,331,244千元</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @5; 600031_三一重工_三一重工股份有限公司2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
@@ -3799,12 +4323,17 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益 = 23.00%</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" s="6" t="inlineStr"/>
       <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
@@ -3840,12 +4369,19 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
+          <t>【万科A 2025年年度报告】经营活动产生的现金流量净额 = (988,124,860.96)
+【万科A 2025年年度报告】扣除非经常性损益后归属于上 市公司股东的净利润 = (85,917,363,120.34)
+扣除非经常性损益后归属于上 市公司股东的净利润 = (45,393,719,289.83)元</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11; 000002_万科A_2025年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" s="6" t="inlineStr"/>
       <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -3881,12 +4417,17 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2022年年度报告.pdf @10; 002415_海康威视_2025年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" s="6" t="inlineStr"/>
       <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
@@ -3920,12 +4461,20 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益（元／股） = 1.34
+稀释每股收益（元／股） = 1.48
+加权平均净资产收益率（%） = 19.23
+扣除非经常性损益后的加权平均净资产收益率（%） = 17.39</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H88" s="6" t="inlineStr"/>
       <c r="I88" s="6" t="inlineStr"/>
       <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
@@ -3959,12 +4508,17 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H89" s="6" t="inlineStr"/>
       <c r="I89" s="6" t="inlineStr"/>
       <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
@@ -4000,12 +4554,18 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经常性 损益的净利润 = -7,361,963,984.28元
+归属于上市公司股东的扣 除非经常性损益的净利润 = -8,747,230,737.94元</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2024年年度报告（修订版）.pdf @11; 601012_隆基绿能_2025年年度报告.pdf @13</t>
         </is>
       </c>
-      <c r="H90" s="6" t="inlineStr"/>
       <c r="I90" s="6" t="inlineStr"/>
       <c r="J90" s="6" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
@@ -4039,12 +4599,17 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净资产 = 197,506,672,396.00元</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H91" s="6" t="inlineStr"/>
       <c r="I91" s="6" t="inlineStr"/>
       <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
@@ -4078,12 +4643,17 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 64,965,662千元</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H92" s="6" t="inlineStr"/>
       <c r="I92" s="6" t="inlineStr"/>
       <c r="J92" s="6" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -4119,12 +4689,20 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东 的扣除非经常性损益 的净利润 = 10,833,665,062.03元
+归属于上市公司股东的 扣除非经常性损益的净 利润 = 14,413,943,218.87元
+归属于上市公司股东 的净资产 = 70,492,311,268.60元
+归属于上市公司股东的 净资产 = 62,146,786,334.37元</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2022年年度报告（修订版）.pdf @9; 601012_隆基绿能_2023年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H93" s="6" t="inlineStr"/>
       <c r="I93" s="6" t="inlineStr"/>
       <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
@@ -4158,12 +4736,20 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股 收益（元／股） = 1.14
+稀释每股收益（元／股） = 1.18
+加权平均净资产收益率（%） = 14.26
+扣除非经常性损益后的加权平均 净资产收益率（%） = 13.71</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H94" s="6" t="inlineStr"/>
       <c r="I94" s="6" t="inlineStr"/>
       <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
@@ -4197,12 +4783,17 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
           <t>000651_格力电器_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H95" s="6" t="inlineStr"/>
       <c r="I95" s="6" t="inlineStr"/>
       <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
@@ -4238,12 +4829,17 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6; 601012_隆基绿能_2023年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H96" s="6" t="inlineStr"/>
       <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="5" t="n">
@@ -4279,12 +4875,17 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净资产 = 40,465,795,358.69元</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6; 600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H97" s="6" t="inlineStr"/>
       <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="5" t="n">
@@ -4320,12 +4921,17 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2022年年度报告.pdf @6; 600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H98" s="6" t="inlineStr"/>
       <c r="I98" s="6" t="inlineStr"/>
       <c r="J98" s="6" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="5" t="n">
@@ -4361,12 +4967,18 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东 的扣除非经常性损益 的净利润 = 10,833,665,062.03元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 9,747,587,804.59元</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2023年年度报告.pdf @11; 603259_药明康德_2023年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H99" s="6" t="inlineStr"/>
       <c r="I99" s="6" t="inlineStr"/>
       <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="5" t="n">
@@ -4402,12 +5014,22 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的每股净 资产 = 9.80
+资产总额 = 1,020,622,831,532.86
+资产负债率 = 76.89%
+归属于上市公司 股东的净利润 = 19,150,582,400.69元
+归属于上市公司 股东的扣除非经 常性损益的净利 润 = 13,240,556,954.42元
+经营活动产生的 现金流量净额 = 17,203,161,622.00元</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2025年年度报告.pdf @11; 603259_药明康德_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H100" s="6" t="inlineStr"/>
       <c r="I100" s="6" t="inlineStr"/>
       <c r="J100" s="6" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -4443,12 +5065,22 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
+          <t>投资活动产生的现金流量净额 = (461,564.21)万元
+筹资活动产生的现金流量净额 = (3,681,316.43)万元
+经营活动现金流入小计 = 32,112,867.05万元
+经营活动现金流出小计 = 31,721,634.66万元
+投资活动现金流入小计 = 1,527,306.06万元
+投资活动现金流出小计 = 1,988,870.27万元</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
           <t>000002_万  科Ａ_2023年年度报告.pdf @29; 002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H101" s="6" t="inlineStr"/>
       <c r="I101" s="6" t="inlineStr"/>
       <c r="J101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="5" t="n">
@@ -4484,12 +5116,22 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 24.13%
+归属于上市公司股东的净利润（千元） = 50,744,682
+经营活动产生的现金流量净额（千元） = 96,990,345
+资产总额（千元） = 786,658,123
+归属于上市公司股东的 净利润 = 7,711,054,811.98元
+归属于上市公司股东的 扣除非经常性损益的净 利润 = 7,413,405,567.05元</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9; 600276_恒瑞医药_恒瑞医药2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H102" s="6" t="inlineStr"/>
       <c r="I102" s="6" t="inlineStr"/>
       <c r="J102" s="6" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -4525,12 +5167,18 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 71,953,244千元
+归属于上市公司股东的净 资产 = 233,105,984,399.47元</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @5; 600519_贵州茅台_贵州茅台2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H103" s="6" t="inlineStr"/>
       <c r="I103" s="6" t="inlineStr"/>
       <c r="J103" s="6" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="5" t="n">
@@ -4566,20 +5214,26 @@
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
+          <t>成本收入比 = 27.66%
+非利息净收入占比 = 36.31%</t>
+        </is>
+      </c>
+      <c r="H104" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2024年年度报告.pdf @16; 002415_海康威视_2025年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H104" s="6" t="inlineStr"/>
       <c r="I104" s="6" t="inlineStr"/>
       <c r="J104" s="6" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:I104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:J104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,存疑"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4593,19 +5247,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4621,7 +5276,8 @@
           <t>填写说明：只需填黄色三列，用下拉选择 ✓ / ✗ / 存疑，有疑问时在备注列写一句原因。第4行为示例行（不计入统计）。请独立判定——不要参考另一位标注者的结果，也不要互相商量，否则一致性系数失去意义。
 【答案正确?】标准答案与原文是否相符（数值、行标签、年份、量纲）。相符✓，不符✗。
 【唯一合理答案?】在问题的字面表述下，标准答案是否是唯一站得住的答案。是✓；若一个称职的分析师可能给出另一个同样站得住的答案，判✗并在备注写出那个答案。常见歧义来源：①指标口径（归母净资产／所有者权益合计、营业收入／营业总收入）；②合并报表与母公司报表；③上年数是追溯调整后还是原披露数；④同一年数字在本年报与次年年报的上年同期栏都出现，取哪一处。
-注意这两列相互独立：答案可以完全正确，但问题本身有歧义（判 ✓ / ✗）。证据原文列是自动匹配的 gold 三元组；表名若读不出计量单位，请对照原PDF确认量纲。
+注意这两列相互独立：答案可以完全正确，但问题本身有歧义。
+【同表相近行】列出了同一张表里口径相近的其他科目及其数值——判歧义时先看这一列，多数情况无需打开源PDF。仅当表名读不出计量单位、或需确认上年数是否追溯调整时，才需对照原PDF。
 本页刻意挑选了核验成本高或存在分歧风险的条目（证据跨表跨页、单位由表名回挂、比率类指标等）。顺序已打散，判定时无需考虑它为何入选。</t>
         </is>
       </c>
@@ -4659,20 +5315,25 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>同表相近行（判歧义用）</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>来源（文件@页）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>答案正确?</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>唯一合理答案?</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -4711,22 +5372,28 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>营业总收入 = 164,699百万元
+利息净收入 = 116,061百万元</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
           <t>000001_平安银行_2023年年度报告.pdf @15</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>数值与原文一致；「营业收入」在该表中口径唯一</t>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>数值与原文一致；该表虽有「营业总收入」，但本行两者同值，不构成歧义</t>
         </is>
       </c>
     </row>
@@ -4762,12 +5429,18 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 62,791,872,697.72元
+归属于上市公司股 东的净资产 = 197,506,672,396.00元</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr"/>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="6" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -4803,12 +5476,19 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 21.34%
+归属于上市公司股东的净资产（元） = 69,327,010,925.99
+归属于上市公司股东的净资产 = 53,179,935,140.80元</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2024年年度报告.pdf @8; 600887_伊利股份_内蒙古伊利实业集团股份有限公司2024年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -4842,12 +5522,17 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净资产 = 197,506,672,396.00元</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="6" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
@@ -4883,12 +5568,17 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6; 600276_恒瑞医药_恒瑞医药2024年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="6" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
@@ -4924,12 +5614,22 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的每股净资产 = 21.00
+全面摊薄净资产收 益率 = 9.32%
+加权平均净资产收 益率 = 9.48%
+加权平均净资产收益率 = 25.28%
+归属于上市公司股 东的净利润 = 22,617,778,516.45元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12; 000858_五 粮 液_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
       <c r="I9" s="6" t="inlineStr"/>
       <c r="J9" s="6" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
@@ -4963,12 +5663,17 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2023年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
@@ -5004,12 +5709,17 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 4,141,262,764.05元</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8; 600276_恒瑞医药_恒瑞医药2023年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
       <c r="I11" s="6" t="inlineStr"/>
       <c r="J11" s="6" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
@@ -5045,12 +5755,22 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 59.51
+扣除非经常性损益后的基本每股 收益（元／股） = 49.99
+稀释每股收益（元／股） = 59.49
+加权平均净资产收益率（%） = 34.19
+扣除非经常性损益后的加权平 均净资产收益率（%） = 34.20
+扣除非经常性损益后的加权平均 净资产收益率（%） = 30.29</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5; 600519_贵州茅台_贵州茅台2023年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr"/>
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
@@ -5086,12 +5806,20 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 9,747,587,804.59元
+归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元
+归属于上市公司股 东的净资产 = 55,122,453,910.73元
+归属于上市公司股东的净 资产 = 46,589,953,393.31元</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7; 603259_药明康德_2023年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" s="6" t="inlineStr"/>
       <c r="J13" s="6" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
@@ -5125,12 +5853,20 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益（元／股） = 1.34
+稀释每股收益（元／股） = 1.48
+加权平均净资产收益率（%） = 19.23
+扣除非经常性损益后的加权平均净资产收益率（%） = 17.39</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
@@ -5164,12 +5900,20 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益 = (4.17)
+扣除非经常性损益后归属于上 市公司股东的净利润 = (45,393,719,289.83)元
+净资产收益率（全面摊薄） = -24.41%
+净资产收益率（加权平均） = -21.82%</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr"/>
       <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
@@ -5203,12 +5947,17 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2025年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
@@ -5242,12 +5991,17 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东 的扣除非经常性损益 的净利润（元） = 8,068,550,808.00</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
           <t>300760_迈瑞医疗_2025年年度报告.pdf @20</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr"/>
       <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
@@ -5281,12 +6035,20 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净 利润 = 8,813,713,033.51元
+归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元
+经营活动产生的现金流量 净额 = 10,616,029,916.68元
+总资产 = 64,690,326,746.96元</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
@@ -5322,12 +6084,17 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2022年年度报告（修订版）.pdf @9; 603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr"/>
       <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
@@ -5361,12 +6128,18 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 21.89
+资产总额 = 5,769,270百万元</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2024年年度报告.pdf @16</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" s="6" t="inlineStr"/>
       <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
@@ -5402,12 +6175,17 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 244,637,811,032.18元</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2025年年度报告.pdf @6; 601012_隆基绿能_2025年年度报告.pdf @13</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" s="6" t="inlineStr"/>
       <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
@@ -5443,12 +6221,20 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 25.28%
+归属于上市公司股东的净利润（元） = 26,690,661,397.42
+经营活动产生的现金流量净额（元） = 24,431,136,261.48
+总资产（元） = 152,714,727,880.22</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7; 002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
@@ -5482,12 +6268,21 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 19,762,103,017.38元
+营业利润 = 52,006,935,659.54元
+利润总额 = 52,386,185,416.63元
+归属于上市公司股 东的净资产 = 242,691,342,204.55元
+归属于上市公司股 东的每股净资产 = 21.00</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr"/>
       <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
@@ -5523,12 +6318,22 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
+          <t>投资活动产生的现金流量净额 = -13,326,365,843.11元
+筹资活动产生的现金流量净额 = 8,156,248,181.45元
+经营活动现金流入小计 = 243,587,978,384.02元
+经营活动现金流出小计 = 230,860,368,064.68元
+投资活动现金流入小计 = 10,037,921,670.41元
+投资活动现金流出小计 = 23,364,287,513.52元</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2022年年度报告.pdf @26; 002475_立讯精密_2024年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
@@ -5562,12 +6367,20 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 2.82
+稀释每股收益（元／股） = 2.82
+加权平均净资产收益率（%） = 20.62
+扣除非经常性损益后的加权平 均净资产收益率（%） = 19.32</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" s="6" t="inlineStr"/>
       <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
@@ -5603,12 +6416,20 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益（元／股） = 1.75
+稀释每股收益（元／股） = 1.83
+加权平均净资产收益率（%） = 20.87
+扣除非经常性损益后的加权平均净资产收益率（%） = 19.97</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2024年年度报告.pdf @7; 600887_伊利股份_内蒙古伊利实业集团股份有限公司2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -5642,12 +6463,17 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2023年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" s="6" t="inlineStr"/>
       <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -5681,12 +6507,17 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（千元） = 162,878,825</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
@@ -5720,12 +6551,20 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净利润 = 82,320,067,101.68元
+归属于上市公司股东的扣除非 经常性损益的净利润 = 82,293,107,655.25元
+经营活动产生的现金流量净额 = 61,522,204,989.35元
+总资产 = 303,834,844,021.44元</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" s="6" t="inlineStr"/>
       <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
@@ -5759,12 +6598,17 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2024年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
@@ -5798,12 +6642,17 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 62,791,872,697.72元</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
       <c r="I31" s="6" t="inlineStr"/>
       <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
@@ -5839,12 +6688,17 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2022年度报告.pdf @7; 601088_中国神华_中国神华2023年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
@@ -5878,12 +6732,18 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 4.92
+加权平均净资产收益率 = 22.23%</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" s="6" t="inlineStr"/>
       <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
@@ -5919,12 +6779,22 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的净利润 = 32,496,172,808.65元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 32,507,551,977.06元
+经营活动产生的现 金流量净额 = 59,648,468,284.22元
+总资产 = 566,071,979,792.34元
+归属于上市公司 股东的净利润 = 27,238,970,860.70元
+归属于上市公司 股东的扣除非经 常性损益的净利 润 = 27,508,231,223.76元</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2023年年度报告.pdf @6; 600900_长江电力_长江电力2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -5958,12 +6828,17 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净 资产 = 46,589,953,393.31元</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
       <c r="I35" s="6" t="inlineStr"/>
       <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -5997,12 +6872,18 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 23.25
+资产总额 = 5,925,777百万元</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2025年年度报告.pdf @17</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
       <c r="I36" s="6" t="inlineStr"/>
       <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
@@ -6038,12 +6919,17 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 111,029,299,000.00</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8; 300760_迈瑞医疗_2023年年度报告.pdf @19</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
       <c r="I37" s="6" t="inlineStr"/>
       <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
@@ -6077,12 +6963,17 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 32,507,551,977.06元</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
@@ -6116,12 +7007,18 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 1.370
+加权平均净资产收益率 = 19.62%</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="6" t="inlineStr"/>
       <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
@@ -6157,12 +7054,20 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 0.5183
+稀释每股收益（元／股） = 0.7058
+加权平均净资产收益率（%） = 6.85
+扣除非经常性损益后的加权平 均净资产收益率（%） = 6.64</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2023年年度报告.pdf @5; 600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
@@ -6196,12 +7101,20 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净利润 = 9,431,064,679.78元
+归属于上市公司股东的扣除非经 常性损益的净利润 = 8,585,692,731.44元
+经营活动产生的现金流量净额 = 13,420,320,580.36元
+总资产 = 130,965,302,299.22元</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
       <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
@@ -6237,12 +7150,17 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 114,025,058,788.17</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7; 002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
@@ -6278,12 +7196,22 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 16.14%
+归属于上市公司股东的净利润（元） = 16,622,448,000.00
+经营活动产生的现金流量净额（元） = 140,837,657,000.00
+总资产（元） = 493,860,646,000.00
+归属于上市公司股东的净 利润 = 8,813,713,033.51元
+归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8; 603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
       <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
@@ -6319,12 +7247,17 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7; 002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
@@ -6360,12 +7293,22 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的每股净 资产 = 17.09
+归属于上市公司股 东的每股净资产 = 21.00
+全面摊薄净资产收 益率 = 9.32%
+加权平均净资产收 益率 = 9.48%
+资产总额 = 1,286,259,859,765.82
+资产负债率 = 73.66%</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2022年年度报告.pdf @12; 000002_万科A_2024年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
       <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
@@ -6399,12 +7342,18 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元
+归属于上市公司股东的净 资产 = 46,589,953,393.31元</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
@@ -6438,12 +7387,17 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2024年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
       <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="n">
@@ -6477,12 +7431,17 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 54,655,690,475.89元</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -6516,12 +7475,20 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平均净资产收益率（%） = 19.36
+基本每股收益（元／股） = 1.64
+稀释每股收益（元／股） = 1.64
+扣除非经常性损益后的基本每股收益（元／股） = 1.57</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2023年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H49" s="6" t="inlineStr"/>
       <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
@@ -6557,12 +7524,17 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7; 601012_隆基绿能_2023年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H50" s="6" t="inlineStr"/>
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -6598,12 +7570,22 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益 （元／股） = 1.3669
+扣除非经常性损益后的基本每 股收益（元／股） = 1.3286
+稀释每股收益（元／股） = 1.4101
+加权平均净资产收益率（%） = 15.90
+扣除非经常性损益后的加权平均净资 产收益率（%） = 15.41
+扣除非经常性损益后的加权平 均净资产收益率（%） = 15.72</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2024年年度报告.pdf @6; 600900_长江电力_长江电力2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H51" s="6" t="inlineStr"/>
       <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
@@ -6639,12 +7621,22 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 18.80
+资产总额 = 5,321,514百万元
+归属于上市公司股 东的净利润 = 62,716,443,738.27元
+归属于上市公司股 东的扣除非经常性 损益的净利润 = 62,791,872,697.72元
+经营活动产生的现 金流量净额 = 36,698,595,830.03元
+总资产 = 254,364,804,995.25元</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2022年年度报告.pdf @18; 600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H52" s="6" t="inlineStr"/>
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -6678,12 +7670,20 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平 均净资产收益率（%） = 34.20
+基本每股收益（元／股） = 59.49
+稀释每股收益（元／股） = 59.49
+扣除非经常性损益后的基本每 股收益（元／股） = 59.51</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2023年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr"/>
       <c r="I53" s="6" t="inlineStr"/>
       <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
@@ -6717,12 +7717,17 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
+          <t>归属于本行普通股股东的每股净资产（元/股） = 18.80</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
           <t>000001_平安银行_2022年年度报告.pdf @18</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr"/>
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
@@ -6756,12 +7761,17 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
           <t>002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr"/>
       <c r="I55" s="6" t="inlineStr"/>
       <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
@@ -6795,12 +7805,18 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 11.58
+加权平均净资产收益率 = 24.13%</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr"/>
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
@@ -6834,12 +7850,17 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr"/>
       <c r="I57" s="6" t="inlineStr"/>
       <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
@@ -6873,12 +7894,18 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 62,791,872,697.72元
+归属于上市公司股 东的净资产 = 197,506,672,396.00元</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
@@ -6914,12 +7941,22 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 22.23%
+归属于上市公司股东的净利润（千元） = 33,719,935
+经营活动产生的现金流量净额（千元） = 57,902,611
+总资产（千元） = 486,038,184
+归属于上市公司股东的净利润（元） = 13,365,651,026.16
+经营活动产生的现金流量净额（元） = 27,116,908,208.53</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10; 002475_立讯精密_2024年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H59" s="6" t="inlineStr"/>
       <c r="I59" s="6" t="inlineStr"/>
       <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
@@ -6955,12 +7992,18 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 11,068,321,695.12元
+归属于上市公司 股东的扣除非经 常性损益的净利 润 = 13,240,556,954.42元</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2025年年度报告.pdf @7; 603259_药明康德_2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr"/>
       <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
@@ -6994,12 +8037,18 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 22.23%
+归属于上市公司股东的净资产（千元） = 162,878,825</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr"/>
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
@@ -7033,12 +8082,18 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 22.23%
+归属于上市公司股东的净资产（千元） = 162,878,825</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr"/>
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
@@ -7074,12 +8129,17 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产（元） = 69,327,010,925.99</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
           <t>002475_立讯精密_2024年年度报告.pdf @8; 002594_比亚迪_2022年年度报告.pdf @8</t>
         </is>
       </c>
-      <c r="H63" s="6" t="inlineStr"/>
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n">
@@ -7113,12 +8173,17 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的净资产 = 64,965,662千元</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H64" s="6" t="inlineStr"/>
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -7154,12 +8219,18 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经常 性损益的净利润 = 3,126,760千元
+归属于上市公司股东的扣 除非经常性损益的净利润 = 8,260,289,685.19元</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5; 603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H65" s="6" t="inlineStr"/>
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n">
@@ -7193,12 +8264,17 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
           <t>300760_迈瑞医疗_2024年年度报告.pdf @21</t>
         </is>
       </c>
-      <c r="H66" s="6" t="inlineStr"/>
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -7234,12 +8310,20 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股 收益（元／股） = -1.16
+稀释每股收益（元／股） = -1.14
+加权平均净资产收益率（%） = -13.10
+扣除非经常性损益后的加权平均 净资产收益率（%） = -13.30</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2023年年度报告.pdf @12; 601012_隆基绿能_2024年年度报告（修订版）.pdf @11</t>
         </is>
       </c>
-      <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="5" t="n">
@@ -7275,12 +8359,19 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后归属于上 市公司股东的净利润 = (45,393,719,289.83)元
+营业利润 = (45,643,796,280.61)元
+利润总额 = (47,186,559,181.39)元</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11; 300760_迈瑞医疗_2024年年度报告.pdf @21</t>
         </is>
       </c>
-      <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
@@ -7316,12 +8407,20 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 0.9616
+稀释每股收益（元／股） = 0.9834
+加权平均净资产收益率（%） = 11.18
+扣除非经常性损益后的加权平 均净资产收益率（%） = 10.93</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2024年年度报告.pdf @5; 600031_三一重工_三一重工股份有限公司2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
@@ -7355,12 +8454,17 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经常 性损益的净利润 = 3,126,760千元</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
           <t>600031_三一重工_三一重工股份有限公司2022年年度报告.pdf @5</t>
         </is>
       </c>
-      <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
@@ -7394,12 +8498,18 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
+          <t>稀释每股收益（元/股） = 6.876
+加权平均净资产收益率 = 25.28%</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
@@ -7435,12 +8545,19 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司 股东的扣除非经 常性损益的净利 润 = 27,508,231,223.76元
+归属于上市公司股东的净资产（千元） = 246,930,033
+归属于上市公司 股东的净资产 = 201,330,025,517.69元</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
           <t>300750_宁德时代_2024年年度报告.pdf @9; 600900_长江电力_长江电力2023年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -7474,12 +8591,18 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 22.23%
+归属于上市公司股东的净资产（千元） = 162,878,825</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
           <t>000333_美的集团_2023年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n">
@@ -7515,12 +8638,20 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非 经常性损益的净利润 = 82,293,107,655.25元
+归属于上市公司股东的扣除非经常性 损益的净利润 = -7,361,963,984.28元
+利润总额 = 114,755,261,605.08元
+归属于上市公司股东的净资产 = 244,637,811,032.18元</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
           <t>600519_贵州茅台_贵州茅台2025年年度报告.pdf @6; 601012_隆基绿能_2025年年度报告.pdf @13</t>
         </is>
       </c>
-      <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
@@ -7554,12 +8685,19 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的每股净 资产 = 17.09
+资产总额 = 1,286,259,859,765.82
+资产负债率 = 73.66%</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
           <t>000002_万科A_2024年年度报告.pdf @11</t>
         </is>
       </c>
-      <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="n">
@@ -7593,12 +8731,17 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
+          <t>扣除与主营业务无关的业 务收入和不具备商业实质 的收入后的营业收入 = 81,211,823,906.59元</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
           <t>601012_隆基绿能_2024年年度报告（修订版）.pdf @11</t>
         </is>
       </c>
-      <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
@@ -7632,12 +8775,20 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每股收益 （元／股） = 1.3669
+稀释每股收益（元／股） = 1.4101
+加权平均净资产收益率（%） = 15.90
+扣除非经常性损益后的加权平均净资 产收益率（%） = 15.41</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2025年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n">
@@ -7671,12 +8822,20 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的加权平均 净资产收益率（%） = 13.71
+基本每股收益（元／股） = 1.19
+稀释每股收益（元／股） = 1.18
+扣除非经常性损益后的基本每股 收益（元／股） = 1.14</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
           <t>600276_恒瑞医药_恒瑞医药2025年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -7710,12 +8869,17 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
+          <t>（同表无口径相近的其他行）</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
           <t>603259_药明康德_2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
       <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="5" t="n">
@@ -7749,12 +8913,18 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股东的扣除非经 常性损益的净利润 = 8,585,692,731.44元
+归属于上市公司股东的净资产 = 50,267,883,832.15元</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
           <t>600887_伊利股份_内蒙古伊利实业集团股份有限公司2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" s="6" t="inlineStr"/>
       <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
@@ -7788,12 +8958,17 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
+          <t>营业成本 = 百万元</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
           <t>601088_中国神华_中国神华2022年度报告.pdf @29</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="6" t="inlineStr"/>
       <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
@@ -7827,12 +9002,18 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
+          <t>归属于上市公司股 东的扣除非经常性 损益的净利润 = 21,392,344,535.58元
+归属于上市公司股 东的净资产 = 185,488,250,616.82元</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2022年年度报告.pdf @6</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" s="6" t="inlineStr"/>
       <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
@@ -7868,12 +9049,20 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
+          <t>加权平均净资产收益率 = 25.28%
+归属于上市公司股东的净利润（元） = 26,690,661,397.42
+经营活动产生的现金流量净额（元） = 24,431,136,261.48
+总资产（元） = 152,714,727,880.22</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
           <t>000858_五 粮 液_2022年年度报告.pdf @7; 002415_海康威视_2022年年度报告.pdf @10</t>
         </is>
       </c>
-      <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
       <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
@@ -7907,20 +9096,28 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
+          <t>扣除非经常性损益后的基本每 股收益（元／股） = 0.9407
+稀释每股收益（元／股） = 0.9370
+加权平均净资产收益率（%） = 11.73
+扣除非经常性损益后的加权平 均净资产收益率（%） = 11.77</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
           <t>600900_长江电力_长江电力2022年年度报告.pdf @7</t>
         </is>
       </c>
-      <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H5:I84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I5:J84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,存疑"</formula1>
     </dataValidation>
   </dataValidations>
